--- a/04_DESIGN_TABLES/DesignTable_2705_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2705_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,12 +829,17 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L24@DRIVE=1.84~1.840; C5HEX@HEX=0.69~0.688; D@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -954,12 +959,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L24@DRIVE=1.84~1.840; C5HEX@HEX=0.69~0.688; D@BORE=0.17~0.172</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1471,11 +1481,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2705-06-06-LN</t>
+          <t>2705-06-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="C9" t="n">
         <v>0.50518</v>
@@ -1505,22 +1515,22 @@
         <v>0.3294</v>
       </c>
       <c r="L9" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="M9" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9755</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="R9" t="n">
         <v>60</v>
@@ -1529,37 +1539,37 @@
         <v>37</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1735</v>
+        <v>1.1038</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2705-06-06-LN</t>
+          <t>2705-06-04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Female Pipe x JIC Bulkhead Connector, 3/8-18 NPTF (female) x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/8-18 NPTF (female) x 7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1574,7 +1584,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>9/16-18 (bulkhead)</t>
+          <t>7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -1584,68 +1594,73 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1060 Overall Length = 2.220 (table had 2.18); C5HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1060 Hex Flat = 0.875 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; L24 / hex / bore: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.8, one source); I1 = Air-Way -04 bulkhead length (A8); tap drill = Air-Way per size (A1); JIC end MS33656J | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L24 / hex / bore from OMi Items (= Brennan TFA p.8), I1 = Air-Way per size (A8)</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2705-LN-06-06</t>
+          <t>2705-06-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2705-08-10</t>
+          <t>2705-06-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.84</v>
+        <v>2.22</v>
       </c>
       <c r="C10" t="n">
-        <v>0.65241</v>
+        <v>0.50518</v>
       </c>
       <c r="D10" t="n">
-        <v>1.13</v>
+        <v>0.875</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J10" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1773</v>
+        <v>0.9755</v>
       </c>
       <c r="O10" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="R10" t="n">
         <v>60</v>
@@ -1654,37 +1669,37 @@
         <v>37</v>
       </c>
       <c r="T10" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4433</v>
+        <v>1.1735</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2705-08-10</t>
+          <t>2705-06-06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Female Pipe x JIC Bulkhead Connector, 1/2-14 NPTF (female) x 7/8-14 (bulkhead)</t>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/8-18 NPTF (female) x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1694,12 +1709,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7/8-14 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -1709,68 +1724,73 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1049 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1046 = 2.220 (table had 2.18) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): C5HEX@HEX 1 -&gt; 0.875</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2705-08-10</t>
+          <t>2705-06-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2705-08-10-LN</t>
+          <t>2705-06-06-LN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.84</v>
+        <v>2.22</v>
       </c>
       <c r="C11" t="n">
-        <v>0.65241</v>
+        <v>0.50518</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13</v>
+        <v>0.875</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9</v>
+        <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J11" t="n">
-        <v>0.35</v>
+        <v>0.285</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4071</v>
+        <v>0.3294</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="M11" t="n">
-        <v>0.107</v>
+        <v>0.083</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1773</v>
+        <v>0.9755</v>
       </c>
       <c r="O11" t="n">
-        <v>0.386</v>
+        <v>0.2405</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1114</v>
+        <v>0.0898</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="R11" t="n">
         <v>60</v>
@@ -1779,37 +1799,37 @@
         <v>37</v>
       </c>
       <c r="T11" t="n">
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="U11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4433</v>
+        <v>1.1735</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03866</v>
+        <v>0.03007</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01786</v>
+        <v>0.01389</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2705-08-10-LN</t>
+          <t>2705-06-06-LN</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Female Pipe x JIC Bulkhead Connector, 1/2-14 NPTF (female) x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/8-18 NPTF (female) x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1819,12 +1839,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7/8-14 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -1834,68 +1854,68 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1063 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1060 Overall Length = 2.220 (table had 2.18); C5HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1060 Hex Flat = 0.875 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2705-LN-08-10</t>
+          <t>2705-LN-06-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2705-12-12</t>
+          <t>2705-06-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="C12" t="n">
-        <v>0.79674</v>
+        <v>0.57735</v>
       </c>
       <c r="D12" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="F12" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="G12" t="n">
-        <v>0.91</v>
+        <v>0.57</v>
       </c>
       <c r="H12" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="J12" t="n">
-        <v>0.455</v>
+        <v>0.285</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5121</v>
+        <v>0.3294</v>
       </c>
       <c r="L12" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="M12" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="N12" t="n">
-        <v>1.2755</v>
+        <v>1.0667</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="R12" t="n">
         <v>60</v>
@@ -1904,37 +1924,37 @@
         <v>37</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5905</v>
+        <v>1.3197</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2705-12-12</t>
+          <t>2705-06-08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Female Pipe x JIC Bulkhead Connector, 3/4-14 NPTF (female) x 1 1/16-12 (bulkhead)</t>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/8-18 NPTF (female) x 3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1944,12 +1964,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>1 1/16-12 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -1959,68 +1979,73 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1050 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1047 = 2.390 (table had 2.34) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2705-12-12</t>
+          <t>2705-06-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2705-12-12-LN</t>
+          <t>2705-08-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.99</v>
+        <v>2.61</v>
       </c>
       <c r="C13" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D13" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="F13" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I13" t="n">
         <v>0.07140000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.455</v>
+        <v>0.35</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5121</v>
+        <v>0.4071</v>
       </c>
       <c r="L13" t="n">
-        <v>0.53125</v>
+        <v>0.375</v>
       </c>
       <c r="M13" t="n">
-        <v>0.125</v>
+        <v>0.094</v>
       </c>
       <c r="N13" t="n">
-        <v>1.2755</v>
+        <v>1.0667</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4715</v>
+        <v>0.3295</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1299</v>
+        <v>0.0984</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="R13" t="n">
         <v>60</v>
@@ -2029,37 +2054,37 @@
         <v>37</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0625</v>
+        <v>0.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5905</v>
+        <v>1.3197</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04511</v>
+        <v>0.03383</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02083</v>
+        <v>0.01562</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.61</v>
+        <v>0.39</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2705-12-12-LN</t>
+          <t>2705-08-08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Female Pipe x JIC Bulkhead Connector, 3/4-14 NPTF (female) x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Female Pipe x JIC Bulkhead Connector, 1/2-14 NPTF (female) x 3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2069,12 +2094,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>1 1/16-12 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2084,68 +2109,73 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1064 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1048 = 2.610 (table had 2.58) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2705-LN-12-12</t>
+          <t>2705-08-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2705-16-16</t>
+          <t>2705-08-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="C14" t="n">
-        <v>0.94108</v>
+        <v>0.65241</v>
       </c>
       <c r="D14" t="n">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="E14" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="L14" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="M14" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="N14" t="n">
-        <v>1.2755</v>
+        <v>1.1773</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="R14" t="n">
         <v>60</v>
@@ -2154,37 +2184,37 @@
         <v>37</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3125</v>
+        <v>0.875</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5905</v>
+        <v>1.4433</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2705-16-16</t>
+          <t>2705-08-10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Female Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF (female) x 1 5/16-12 (bulkhead)</t>
+          <t>Female Pipe x JIC Bulkhead Connector, 1/2-14 NPTF (female) x 7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2194,12 +2224,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF (female)</t>
+          <t>1/2-14 NPTF (female)</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>1 5/16-12 (bulkhead)</t>
+          <t>7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -2209,68 +2239,68 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1052 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1049 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2705-16-16</t>
+          <t>2705-08-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2705-16-16-LN</t>
+          <t>2705-08-10-LN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.23</v>
+        <v>2.84</v>
       </c>
       <c r="C15" t="n">
-        <v>0.94108</v>
+        <v>0.65241</v>
       </c>
       <c r="D15" t="n">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="E15" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="F15" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
-        <v>1.14</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.14</v>
+        <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="L15" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="M15" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="N15" t="n">
-        <v>1.2755</v>
+        <v>1.1773</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5965</v>
+        <v>0.386</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1292</v>
+        <v>0.1114</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1858</v>
+        <v>0.1546</v>
       </c>
       <c r="R15" t="n">
         <v>60</v>
@@ -2279,65 +2309,565 @@
         <v>37</v>
       </c>
       <c r="T15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4433</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.03866</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2705-08-10-LN</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Female Pipe x JIC Bulkhead Connector, 1/2-14 NPTF (female) x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>7/8-14 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1063 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>2705-LN-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2705-12-12</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.2755</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="R16" t="n">
+        <v>60</v>
+      </c>
+      <c r="S16" t="n">
+        <v>37</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.5905</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2705-12-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/4-14 NPTF (female) x 1 1/16-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1050 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>2705-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2705-12-12-LN</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.2755</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="R17" t="n">
+        <v>60</v>
+      </c>
+      <c r="S17" t="n">
+        <v>37</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.5905</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2705-12-12-LN</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/4-14 NPTF (female) x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1064 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>2705-LN-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2705-16-16</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.94108</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.2755</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="R18" t="n">
+        <v>60</v>
+      </c>
+      <c r="S18" t="n">
+        <v>37</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.3125</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U18" t="n">
         <v>0.08333</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V18" t="n">
         <v>1.5905</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W18" t="n">
         <v>0.04511</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X18" t="n">
         <v>0.02083</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y18" t="n">
         <v>0.08333</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z18" t="n">
         <v>0.84</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA18" t="n">
         <v>2.09</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2705-16-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Female Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF (female) x 1 5/16-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1052 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>2705-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2705-16-16-LN</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="B19" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.94108</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.2755</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="R19" t="n">
+        <v>60</v>
+      </c>
+      <c r="S19" t="n">
+        <v>37</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.5905</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2705-16-16-LN</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Female Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF (female) x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>2705</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>1-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>1 5/16-12 (bulkhead)</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1066 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>2705-LN-16-16</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_2705_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2705_SW2.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C2" t="n">
         <v>0.65241</v>
@@ -675,7 +675,7 @@
         <v>0.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -709,7 +709,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1062 Overall Length = 2.610 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1062 Overall Length = 2.610 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.61 -&gt; Air-Way 2.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -985,7 +990,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>0.43301</v>
@@ -1060,7 +1065,7 @@
         <v>0.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1094,7 +1099,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1043 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1043 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1110,7 +1120,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>0.43301</v>
@@ -1185,7 +1195,7 @@
         <v>0.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1219,7 +1229,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1057 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1057 Overall Length = 2.080 (table had 2) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1235,7 +1250,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="C7" t="n">
         <v>0.46765</v>
@@ -1310,7 +1325,7 @@
         <v>0.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1344,7 +1359,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1044 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1044 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.17 -&gt; Air-Way 2.08</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1360,7 +1380,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="C8" t="n">
         <v>0.46765</v>
@@ -1435,7 +1455,7 @@
         <v>0.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1469,7 +1489,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1058 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1058 Overall Length = 2.170 (table had 2.08) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.08 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.17 -&gt; Air-Way 2.08</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1615,13 +1640,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="C10" t="n">
-        <v>0.50518</v>
+        <v>0.57735</v>
       </c>
       <c r="D10" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0.57</v>
@@ -1690,7 +1715,7 @@
         <v>0.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -1724,12 +1749,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: Air-Way 2.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.22) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C5HEX@HEX: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1046 = 2.220 (table had 2.18) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): C5HEX@HEX 1 -&gt; 0.875</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1046 = 2.220 (table had 2.18) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): C5HEX@HEX 1 -&gt; 0.875 | 2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.22 -&gt; Air-Way 2.18 | 2026-10-20 Air-Way first: C5HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 1</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1745,13 +1770,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.50518</v>
+        <v>0.57735</v>
       </c>
       <c r="D11" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0.57</v>
@@ -1820,7 +1845,7 @@
         <v>0.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -1854,7 +1879,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1060 Overall Length = 2.220 (table had 2.18); C5HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1060 Hex Flat = 0.875 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1060 Overall Length = 2.220 (table had 2.18); C5HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1060 Hex Flat = 0.875 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.22) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C5HEX@HEX: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.22 -&gt; Air-Way 2.18 | 2026-10-20 Air-Way first: C5HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 1</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1870,7 +1900,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="C12" t="n">
         <v>0.57735</v>
@@ -1945,7 +1975,7 @@
         <v>0.39</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -1979,12 +2009,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: Air-Way 2.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.39) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1047 = 2.390 (table had 2.34) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1047 = 2.390 (table had 2.34) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | 2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.39 -&gt; Air-Way 2.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2000,7 +2030,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="C13" t="n">
         <v>0.65241</v>
@@ -2075,7 +2105,7 @@
         <v>0.39</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -2109,12 +2139,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows) | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: Air-Way 2.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1048 = 2.610 (table had 2.58) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | OMi dims first (user 2026-09-25): L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1048 = 2.610 (table had 2.58) | Brennan TFA TFA-p008-t04: agrees on L24@DRIVE, D@BORE | 2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.61 -&gt; Air-Way 2.58</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2130,7 +2160,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="C14" t="n">
         <v>0.65241</v>
@@ -2205,7 +2235,7 @@
         <v>0.48</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -2239,7 +2269,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1049 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1049 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.66 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.84) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.84 -&gt; Air-Way 2.66</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2255,7 +2290,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="C15" t="n">
         <v>0.65241</v>
@@ -2330,7 +2365,7 @@
         <v>0.48</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -2364,7 +2399,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1063 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1063 Overall Length = 2.840 (table had 2.66) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.66 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.84) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.84 -&gt; Air-Way 2.66</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2380,7 +2420,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="C16" t="n">
         <v>0.79674</v>
@@ -2455,7 +2495,7 @@
         <v>0.61</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -2489,7 +2529,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1050 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1050 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.92 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.99 -&gt; Air-Way 2.92</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2505,7 +2550,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="C17" t="n">
         <v>0.79674</v>
@@ -2580,7 +2625,7 @@
         <v>0.61</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -2614,7 +2659,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1064 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1064 Overall Length = 2.990 (table had 2.92) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 2.92 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.99) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 2.99 -&gt; Air-Way 2.92</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2630,7 +2680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="C18" t="n">
         <v>0.94108</v>
@@ -2705,7 +2755,7 @@
         <v>0.84</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -2739,7 +2789,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1052 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1052 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 3.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 3.23 -&gt; Air-Way 3.09</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2755,7 +2810,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="C19" t="n">
         <v>0.94108</v>
@@ -2830,7 +2885,7 @@
         <v>0.84</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -2864,7 +2919,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1066 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+          <t>Air-Way s73 only (double-pass 21 rows); L24@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1066 Overall Length = 3.230 (table had 3.09) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L24@DRIVE: Air-Way 3.09 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L24@DRIVE OMi/Brennan 3.23 -&gt; Air-Way 3.09</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2705_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2705_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2930,6 +2930,136 @@
       <c r="AJ19" t="inlineStr">
         <is>
           <t>2705-LN-16-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2705-LN-06-04</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="R20" t="n">
+        <v>60</v>
+      </c>
+      <c r="S20" t="n">
+        <v>37</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.1038</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2705-LN-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Female Pipe x JIC Bulkhead Connector, 3/8-18 NPTF (female) x 7/16-20 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>7/16-20 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L24 / hex / D = OMi WebsitePartsInfo2026.xlsx Items row 1059 (own -LN row; = the plain 2705-06-04); I1 1.20 = Air-Way -04 bulkhead (A8); tap drill 0.57 = Air-Way -06 (A1); -LN modelled as the plain part, no locknut (A10); thread majors from the end library | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 and 2705-08-08 STEPs), helical thread over P1; JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore D from the bulkhead tip to the pocket bottom; Brennan 2705-08-08: hex 1.13 long carries the port, overall 2.61 (Air-Way L24 2.58)</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1059 + A8 I1 / A1 tap drill / A10 (-LN = the plain part, values equal the plain 2705-06-04 row)</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>2705-LN-06-04</t>
         </is>
       </c>
     </row>
